--- a/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,24</t>
+          <t>-0,49; 4,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,73</t>
+          <t>-2,56; 1,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,86</t>
+          <t>-3,18; 1,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,33</t>
+          <t>-3,38; 1,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 182,5</t>
+          <t>-12,27; 165,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,54; 48,87</t>
+          <t>-44,77; 57,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,48; 54,2</t>
+          <t>-51,27; 44,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-79,64; 230,12</t>
+          <t>-80,65; 181,44</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,98</t>
+          <t>-1,67; 2,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,53</t>
+          <t>-0,38; 3,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,34</t>
+          <t>-1,44; 2,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,91</t>
+          <t>-0,83; 1,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 62,51</t>
+          <t>-23,5; 60,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 97,19</t>
+          <t>-8,28; 97,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 83,87</t>
+          <t>-31,1; 74,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 212,45</t>
+          <t>-35,78; 202,06</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,44</t>
+          <t>-0,25; 4,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,12</t>
+          <t>0,58; 6,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,08</t>
+          <t>-2,12; 3,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,24</t>
+          <t>-2,38; 2,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 167,15</t>
+          <t>-6,16; 168,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 129,43</t>
+          <t>4,97; 131,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 69,04</t>
+          <t>-28,43; 65,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,43; 102,39</t>
+          <t>-60,75; 114,48</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,84</t>
+          <t>-1,5; 2,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,1</t>
+          <t>-0,67; 3,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,26</t>
+          <t>-1,13; 2,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,57</t>
+          <t>-1,61; 1,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 64,45</t>
+          <t>-23,02; 56,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 95,95</t>
+          <t>-13,06; 102,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 89,78</t>
+          <t>-27,08; 84,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 81,09</t>
+          <t>-42,9; 84,27</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,26</t>
+          <t>-0,08; 2,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,45</t>
+          <t>0,3; 2,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,22</t>
+          <t>-0,74; 1,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,06</t>
+          <t>-0,74; 1,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 52,72</t>
+          <t>-1,31; 51,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 57,46</t>
+          <t>5,6; 59,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 32,01</t>
+          <t>-15,54; 35,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 59,69</t>
+          <t>-25,67; 63,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-4,78%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,15</t>
+          <t>-0,4; 4,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,92</t>
+          <t>-2,7; 1,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,53</t>
+          <t>-2,95; 1,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 1,25</t>
+          <t>-2,15; 1,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 165,78</t>
+          <t>-11,41; 163,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 57,5</t>
+          <t>-46,72; 55,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,27; 44,8</t>
+          <t>-50,44; 54,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-80,65; 181,44</t>
+          <t>-65,03; 206,61</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>-9,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,91</t>
+          <t>-1,57; 3,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 3,56</t>
+          <t>-0,44; 3,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,0</t>
+          <t>-1,48; 1,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,85</t>
+          <t>-1,84; 0,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 60,95</t>
+          <t>-22,69; 65,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 97,48</t>
+          <t>-6,73; 104,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 74,75</t>
+          <t>-32,9; 66,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 202,06</t>
+          <t>-49,83; 47,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,28</t>
+          <t>-0,32; 4,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,23</t>
+          <t>0,77; 6,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 3,0</t>
+          <t>-2,24; 2,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,57</t>
+          <t>-0,58; 4,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 168,99</t>
+          <t>-8,72; 170,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 131,35</t>
+          <t>9,89; 127,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 65,07</t>
+          <t>-30,98; 61,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,75; 114,48</t>
+          <t>-13,57; 167,47</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,74</t>
+          <t>-1,59; 2,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,22</t>
+          <t>-0,41; 3,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,18</t>
+          <t>-1,03; 2,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,59</t>
+          <t>-1,19; 1,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 56,37</t>
+          <t>-23,99; 57,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 102,58</t>
+          <t>-9,13; 107,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 84,44</t>
+          <t>-24,6; 89,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,9; 84,27</t>
+          <t>-32,2; 83,49</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,21</t>
+          <t>0,06; 2,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,51</t>
+          <t>0,21; 2,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,39</t>
+          <t>-0,78; 1,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,12</t>
+          <t>-0,29; 1,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 51,23</t>
+          <t>1,01; 52,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,6; 59,0</t>
+          <t>3,55; 58,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 35,87</t>
+          <t>-16,12; 32,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 63,23</t>
+          <t>-9,19; 61,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
